--- a/output/IMG_9692.xlsx
+++ b/output/IMG_9692.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="課別基準客先別売上粗利 202621～2026228" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -609,7 +609,11 @@
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>課別基準客先別売上粗利 2026/2/1～2026/2/28</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
@@ -704,7 +708,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>(株)ジュン</t>
+          <t>㈱ジュン</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -850,7 +854,7 @@
       </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
-          <t>2,384,000</t>
+          <t>2,364,000</t>
         </is>
       </c>
     </row>
@@ -916,7 +920,7 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>(株)エミネント</t>
+          <t>㈱エミネント</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -964,7 +968,7 @@
       <c r="A9" s="12" t="n"/>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>ン11</t>
+          <t>シ11</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -1128,7 +1132,7 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>(株)シーティー・アソシエイツ</t>
+          <t>㈱シーティー・アソシエイツ</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -1181,7 +1185,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>(株)ギャルソンヌ</t>
+          <t>㈱ギャルソンヌ</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -1234,7 +1238,7 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>(株)東京ソワール</t>
+          <t>㈱東京ソワール</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -1340,7 +1344,7 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>(株)アイネックス</t>
+          <t>㈱アイネックス</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -1393,7 +1397,7 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>(株)ユミカツラインターナショナル</t>
+          <t>㈱ユミカツラインターナショナル</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
@@ -1441,7 +1445,7 @@
       <c r="A18" s="12" t="n"/>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>ン58</t>
+          <t>シ58</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -1499,7 +1503,7 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>(株)EGBA</t>
+          <t>㈱EGBA</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
@@ -1552,7 +1556,7 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>(株)守屋</t>
+          <t>㈱守屋</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
@@ -1605,7 +1609,7 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>(株)ダイドーフォワード</t>
+          <t>㈱ダイドーフォワード</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
@@ -1658,7 +1662,7 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>(株)スポーティフ</t>
+          <t>㈱スポーティフ</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
@@ -1695,7 +1699,7 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>(株)リーガルコーポレーション</t>
+          <t>㈱リーガルコーポレーション</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
@@ -1854,7 +1858,7 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>(有)ライディングハイ</t>
+          <t>㈲ライディングハイ</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -1928,7 +1932,7 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>(有)モディスト</t>
+          <t>㈲モディスト</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
@@ -2029,7 +2033,7 @@
       <c r="A30" s="12" t="n"/>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>ン97</t>
+          <t>シ97</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -2087,7 +2091,7 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>(株)スズショウ・アンナ</t>
+          <t>㈱スズショウ・アンナ</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
@@ -2119,7 +2123,7 @@
       <c r="A32" s="12" t="n"/>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>ン51</t>
+          <t>シ51</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -2214,7 +2218,7 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>(株)金万（ストックマン含む）</t>
+          <t>㈱金万(ストックマン含む)</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
@@ -2267,7 +2271,7 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>粋都(上海)時裝商貿有限公司</t>
+          <t>粋都(上海)時装商貿有限公司</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
@@ -2304,7 +2308,7 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>(有)トライシーブス</t>
+          <t>㈲トライシープス</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
@@ -2447,7 +2451,7 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>(株)イデムインターナショナル</t>
+          <t>㈱イテムインターナショナル</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
@@ -2500,7 +2504,7 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>(株)ヤマニ</t>
+          <t>㈱ヤマニ</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
@@ -2549,7 +2553,7 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>(株)ルック</t>
+          <t>㈱ルック</t>
         </is>
       </c>
       <c r="D41" s="14" t="inlineStr">
@@ -2558,9 +2562,9 @@
         </is>
       </c>
       <c r="E41" s="14" t="n"/>
-      <c r="F41" s="14" t="inlineStr">
-        <is>
-          <t>0.0</t>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -2593,7 +2597,7 @@
       <c r="A42" s="12" t="n"/>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>ン15</t>
+          <t>シ15</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">

--- a/output/IMG_9692.xlsx
+++ b/output/IMG_9692.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>㈱ジュン</t>
+          <t>(株)ジュン</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>㈱エミネント</t>
+          <t>(株)エミネント</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>㈱シーティー・アソシエイツ</t>
+          <t>(株)シーティー・アソシエイツ</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>㈱ギャルソンヌ</t>
+          <t>(株)ギャルソヌ</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>㈱東京ソワール</t>
+          <t>(株)東京ソワール</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>㈱アイネックス</t>
+          <t>(株)アイネックス</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>㈱ユミカツラインターナショナル</t>
+          <t>(株)ユミカツラインターナショナル</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>㈱EGBA</t>
+          <t>(株)EGBA</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>㈱守屋</t>
+          <t>(株)守屋</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>㈱ダイドーフォワード</t>
+          <t>(株)ダイドーフォワード</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>㈱スポーティフ</t>
+          <t>(株)スポーティフ</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
@@ -1684,10 +1684,14 @@
       <c r="H22" s="14" t="n"/>
       <c r="I22" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
           <t>147,850</t>
         </is>
       </c>
-      <c r="J22" s="14" t="n"/>
       <c r="K22" s="15" t="n"/>
     </row>
     <row r="23" ht="13" customHeight="1">
@@ -1699,7 +1703,7 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>㈱リーガルコーポレーション</t>
+          <t>(株)リーガルコーポレーション</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
@@ -1858,7 +1862,7 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>㈲ライディングハイ</t>
+          <t>(有)ライディングハイ</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -1890,7 +1894,7 @@
       <c r="A27" s="12" t="n"/>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>サ32</t>
+          <t>ザ32</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -1932,7 +1936,7 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>㈲モディスト</t>
+          <t>(有)モディスト</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
@@ -2091,7 +2095,7 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>㈱スズショウ・アンナ</t>
+          <t>(株)スズショウ・アンナ</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
@@ -2218,7 +2222,7 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>㈱金万(ストックマン含む)</t>
+          <t>(株)金万(ストックマン含む)</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
@@ -2271,7 +2275,7 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>粋都(上海)時装商貿有限公司</t>
+          <t>幹都(上海)時装商貿有限公司</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
@@ -2308,7 +2312,7 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>㈲トライシープス</t>
+          <t>(有)トライシーブス</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
@@ -2451,7 +2455,7 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>㈱イテムインターナショナル</t>
+          <t>(株)イデムインターナショナル</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
@@ -2504,7 +2508,7 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>㈱ヤマニ</t>
+          <t>(株)ヤマニ</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
@@ -2553,7 +2557,7 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>㈱ルック</t>
+          <t>(株)ルック</t>
         </is>
       </c>
       <c r="D41" s="14" t="inlineStr">
@@ -2562,9 +2566,9 @@
         </is>
       </c>
       <c r="E41" s="14" t="n"/>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t>-1.5</t>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">

--- a/output/IMG_9692.xlsx
+++ b/output/IMG_9692.xlsx
@@ -658,7 +658,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>総売上金額</t>
+          <t>純売上金額</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>(株)ギャルソヌ</t>
+          <t>(株)ギャルソンヌ</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>(有)トライシーブス</t>
+          <t>(有)トライシープス</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">

--- a/output/IMG_9692.xlsx
+++ b/output/IMG_9692.xlsx
@@ -28,36 +28,31 @@
     <font>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="10"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="8"/>
+      <sz val="10"/>
     </font>
     <font>
       <color rgb="00000000"/>
-      <sz val="8"/>
+      <sz val="10"/>
     </font>
     <font>
       <color rgb="00FF0000"/>
-      <sz val="8"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -66,166 +61,37 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="medium"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="medium"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="medium"/>
-      <top/>
-      <bottom style="medium"/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="medium"/>
-      <top/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -592,23 +458,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.09" customWidth="1" min="1" max="1"/>
-    <col width="9.09" customWidth="1" min="2" max="2"/>
-    <col width="42.36" customWidth="1" min="3" max="3"/>
-    <col width="18.18" customWidth="1" min="4" max="4"/>
-    <col width="9.09" customWidth="1" min="5" max="5"/>
-    <col width="9.09" customWidth="1" min="6" max="6"/>
-    <col width="18.18" customWidth="1" min="7" max="7"/>
-    <col width="9.09" customWidth="1" min="8" max="8"/>
-    <col width="18.18" customWidth="1" min="9" max="9"/>
-    <col width="18.18" customWidth="1" min="10" max="10"/>
-    <col width="18.18" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14" customHeight="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>課別基準客先別売上粗利 2026/2/1～2026/2/28</t>
@@ -625,2090 +491,2087 @@
       <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
     </row>
-    <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>2026/6/22 10:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>部門名</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>基準客</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>基準客名</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>営業粗利額</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>営業粗利率</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>目標粗利額達成率</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>純売上金額</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>目標売上額達成率</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>在庫金額</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>目標粗利額</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>目標売上額</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="14" customHeight="1">
-      <c r="A3" s="5" t="n"/>
-      <c r="B3" s="6" t="n"/>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-      <c r="I3" s="6" t="n"/>
-      <c r="J3" s="6" t="n"/>
-      <c r="K3" s="7" t="n"/>
-    </row>
-    <row r="4" ht="13" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>1課</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>シ50</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>(株)ジュン</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>6,008,094</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>35.2</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>66.8</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>17,024,012</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>68.7</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>31,270,029</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>8,984,250</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>24,750,000</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>シ13</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>大久保担当その他</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>838,120</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>41.4</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>96.6</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>2,024,436</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>93.3</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>880,036</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>867,600</t>
         </is>
       </c>
-      <c r="K5" s="15" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>2,169,000</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="12" t="n"/>
-      <c r="B6" s="13" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>ア35</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>アイア(株)</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>838,057</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>40.7</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>95.8</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>2,056,248</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>86.9</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>2,401,757</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>874,680</t>
         </is>
       </c>
-      <c r="K6" s="15" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>2,364,000</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="13" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>シ90</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>関谷担当その他②</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>429,606</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>43.6</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>983,653</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>60.4</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>707,653</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>650,800</t>
         </is>
       </c>
-      <c r="K7" s="15" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>1,627,000</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="13" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>エ03</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>(株)エミネント</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>357,900</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>48.7</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>315.3</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>734,205</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>323.4</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>160,835</t>
         </is>
       </c>
-      <c r="J8" s="14" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>113,500</t>
         </is>
       </c>
-      <c r="K8" s="15" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>227,000</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="13" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>シ11</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>泉担当その他</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>353,075</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>49.1</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>94.1</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>717,892</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>86.1</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>374,985</t>
         </is>
       </c>
-      <c r="K9" s="15" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>833,300</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>ヒ50</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>ト50</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>B STONE(株)</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>342,474</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>29.4</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>60.3</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>1,161,649</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>85.9</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>4,729,891</t>
         </is>
       </c>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>567,840</t>
         </is>
       </c>
-      <c r="K10" s="15" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>1,352,000</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="13" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>ア13</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>et maison(株)</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>336,911</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>48.9</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>134.7</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>688,073</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>137.6</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>867,262</t>
         </is>
       </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>250,000</t>
         </is>
       </c>
-      <c r="K11" s="15" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>500,000</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>シ03</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>(株)シーティー・アソシエイツ</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>314,047</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>39.7</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>157.2</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>790,689</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>190.0</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>199,680</t>
         </is>
       </c>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>416,000</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="13" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>キ70</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>(株)ギャルソンヌ</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>(株)ギャルソヌ</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>224,786</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>67.2</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>151.2</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>334,026</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>182.5</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>148,596</t>
         </is>
       </c>
-      <c r="K13" s="15" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>183,000</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="13" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>ト78</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>(株)東京ソワール</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>219,443</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>33.4</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>123.1</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>656,520</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>99.4</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>1,499,678</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>178,200</t>
         </is>
       </c>
-      <c r="K14" s="15" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>660,000</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="13" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>マ50</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>タキヒヨー(株)</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>204,607</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>49.0</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>111.5</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>416,741</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>107.9</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>860,986</t>
         </is>
       </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>183,350</t>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>386,000</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="13" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>ア23</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>(株)アイネックス</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>203,731</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>42.9</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>64.1</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>474,864</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>61.5</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>899,766</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>317,652</t>
         </is>
       </c>
-      <c r="K16" s="15" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>771,000</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="13" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>ユ30</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>(株)ユミカツラインターナショナル</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>190,149</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>39.7</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>98.2</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>478,283</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>89.7</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>376,727</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>193,479</t>
         </is>
       </c>
-      <c r="K17" s="15" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>533,000</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="13" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>シ58</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>東担当その他①</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>156,994</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>39.6</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>44.4</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>395,605</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>44.8</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>48,819</t>
         </is>
       </c>
-      <c r="J18" s="14" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>352,800</t>
         </is>
       </c>
-      <c r="K18" s="15" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>882,000</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="13" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>シ92</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>(株)EGBA</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>117,155</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>37.7</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>58.7</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>310,688</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>54.5</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>781,446</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>199,500</t>
         </is>
       </c>
-      <c r="K19" s="15" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>570,000</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="13" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>モ15</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>(株)守屋</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>98,707</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>41.7</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>116.3</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>236,505</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>117.0</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>227,583</t>
         </is>
       </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>84,840</t>
         </is>
       </c>
-      <c r="K20" s="15" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>202,000</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="12" t="n"/>
-      <c r="B21" s="13" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>ニ42</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>(株)ダイドーフォワード</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>60,708</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>40.5</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>38.7</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>149,720</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>38.1</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>61,491</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>156,800</t>
         </is>
       </c>
-      <c r="K21" s="15" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>392,000</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="13" customHeight="1">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="13" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>ス15</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>(株)スポーティフ</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>60,528</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>43.9</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>137,581</t>
         </is>
       </c>
-      <c r="H22" s="14" t="n"/>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>147,850</t>
         </is>
       </c>
-      <c r="K22" s="15" t="n"/>
-    </row>
-    <row r="23" ht="13" customHeight="1">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="K24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>ニ39</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>(株)リーガルコーポレーション</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>58,078</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>37.6</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>132.7</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>154,215</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>123.3</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>135,087</t>
         </is>
       </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>43,750</t>
         </is>
       </c>
-      <c r="K23" s="15" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>125,000</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="13" customHeight="1">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="13" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>ナ20</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>ナラカミーチェジャパン(株)</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>49,588</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>56.7</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>52.7</t>
         </is>
       </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>87,371</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>34.3</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>59,768</t>
         </is>
       </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>93,980</t>
         </is>
       </c>
-      <c r="K24" s="15" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>254,000</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="13" customHeight="1">
-      <c r="A25" s="12" t="n"/>
-      <c r="B25" s="13" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>エ71</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>越前屋多崎(株)</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>46,200</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>43.7</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>962.5</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>105,550</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>879.5</t>
         </is>
       </c>
-      <c r="I25" s="14" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J25" s="14" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="K25" s="15" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>12,000</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="13" customHeight="1">
-      <c r="A26" s="12" t="n"/>
-      <c r="B26" s="13" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>オ20</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>(有)ライディングハイ</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>40,734</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>39.5</t>
         </is>
       </c>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>103,068</t>
         </is>
       </c>
-      <c r="H26" s="14" t="n"/>
-      <c r="I26" s="14" t="inlineStr">
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J26" s="14" t="n"/>
-      <c r="K26" s="15" t="n"/>
-    </row>
-    <row r="27" ht="13" customHeight="1">
-      <c r="A27" s="12" t="n"/>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>ザ32</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>新規市場開拓(モチフク)</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>30,490</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>25.4</t>
         </is>
       </c>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>120,000</t>
         </is>
       </c>
-      <c r="H27" s="14" t="n"/>
-      <c r="I27" s="14" t="inlineStr">
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J27" s="14" t="n"/>
-      <c r="K27" s="15" t="n"/>
-    </row>
-    <row r="28" ht="13" customHeight="1">
-      <c r="A28" s="12" t="n"/>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>キ13</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>(有)モディスト</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>28,571</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>46.6</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>104.1</t>
         </is>
       </c>
-      <c r="G28" s="14" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>61,230</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>109.3</t>
         </is>
       </c>
-      <c r="I28" s="14" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J28" s="14" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>27,440</t>
         </is>
       </c>
-      <c r="K28" s="15" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>56,000</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="13" customHeight="1">
-      <c r="A29" s="12" t="n"/>
-      <c r="B29" s="13" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>ト70</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>㈱JUNIOR</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>24,951</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>17.9</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>138,983</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>75.5</t>
         </is>
       </c>
-      <c r="I29" s="14" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>625,179</t>
         </is>
       </c>
-      <c r="J29" s="14" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>58,880</t>
         </is>
       </c>
-      <c r="K29" s="15" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>184,000</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="13" customHeight="1">
-      <c r="A30" s="12" t="n"/>
-      <c r="B30" s="13" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>シ97</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>金柿担当その他</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>20,569</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>43.9</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>46,778</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>28.0</t>
         </is>
       </c>
-      <c r="I30" s="14" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J30" s="14" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>99,996</t>
         </is>
       </c>
-      <c r="K30" s="15" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>166,660</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="13" customHeight="1">
-      <c r="A31" s="12" t="n"/>
-      <c r="B31" s="13" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>ス40</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>(株)スズショウ・アンナ</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>18,544</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>41.6</t>
         </is>
       </c>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>44,552</t>
         </is>
       </c>
-      <c r="H31" s="14" t="n"/>
-      <c r="I31" s="14" t="inlineStr">
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J31" s="14" t="n"/>
-      <c r="K31" s="15" t="n"/>
-    </row>
-    <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="12" t="n"/>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>シ51</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>一課その他</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>17,537</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>40.9</t>
         </is>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>42,785</t>
         </is>
       </c>
-      <c r="H32" s="14" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="I32" s="14" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J32" s="14" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>85,696</t>
         </is>
       </c>
-      <c r="K32" s="15" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>208,000</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="13" customHeight="1">
-      <c r="A33" s="12" t="n"/>
-      <c r="B33" s="13" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>キ06</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>キウチ(株)</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>14,040</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>39.0</t>
         </is>
       </c>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>36,000</t>
         </is>
       </c>
-      <c r="H33" s="14" t="n"/>
-      <c r="I33" s="14" t="inlineStr">
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J33" s="14" t="n"/>
-      <c r="K33" s="15" t="n"/>
-    </row>
-    <row r="34" ht="13" customHeight="1">
-      <c r="A34" s="12" t="n"/>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>ス28</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>(株)金万(ストックマン含む)</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>10,847</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>38.3</t>
         </is>
       </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>13.5</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>28,278</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>12.6</t>
         </is>
       </c>
-      <c r="I34" s="14" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>9,350</t>
         </is>
       </c>
-      <c r="J34" s="14" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>80,280</t>
         </is>
       </c>
-      <c r="K34" s="15" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>223,000</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="12" t="n"/>
-      <c r="B35" s="13" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>シ30</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>幹都(上海)時装商貿有限公司</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>10,642</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="F35" s="14" t="n"/>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>17,479</t>
         </is>
       </c>
-      <c r="H35" s="14" t="n"/>
-      <c r="I35" s="14" t="inlineStr">
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J35" s="14" t="n"/>
-      <c r="K35" s="15" t="n"/>
-    </row>
-    <row r="36" ht="13" customHeight="1">
-      <c r="A36" s="12" t="n"/>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>テ10</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>(有)トライシープス</t>
         </is>
       </c>
-      <c r="D36" s="14" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>9,630</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>36.6</t>
         </is>
       </c>
-      <c r="F36" s="14" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>36.1</t>
         </is>
       </c>
-      <c r="G36" s="14" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>26,300</t>
         </is>
       </c>
-      <c r="H36" s="14" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>39.4</t>
         </is>
       </c>
-      <c r="I36" s="14" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J36" s="14" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>26,664</t>
         </is>
       </c>
-      <c r="K36" s="15" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>66,660</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="13" customHeight="1">
-      <c r="A37" s="12" t="n"/>
-      <c r="B37" s="13" t="inlineStr">
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>ホ07</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>ホットマン(株)</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>5,770</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>37.2</t>
         </is>
       </c>
-      <c r="F37" s="14" t="n"/>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>15,500</t>
         </is>
       </c>
-      <c r="H37" s="14" t="n"/>
-      <c r="I37" s="14" t="inlineStr">
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J37" s="14" t="n"/>
-      <c r="K37" s="15" t="n"/>
-    </row>
-    <row r="38" ht="13" customHeight="1">
-      <c r="A38" s="12" t="n"/>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>シ95</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>キャスコ(株)</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>4,045</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>42.4</t>
         </is>
       </c>
-      <c r="F38" s="14" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>9,528</t>
         </is>
       </c>
-      <c r="H38" s="14" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="I38" s="14" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>669,990</t>
         </is>
       </c>
-      <c r="J38" s="14" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>150,000</t>
         </is>
       </c>
-      <c r="K38" s="15" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>375,000</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="13" customHeight="1">
-      <c r="A39" s="12" t="n"/>
-      <c r="B39" s="13" t="inlineStr">
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>イ16</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>(株)イデムインターナショナル</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>894</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>35.9</t>
         </is>
       </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>2,486</t>
         </is>
       </c>
-      <c r="H39" s="14" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="I39" s="14" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>1,870,782</t>
         </is>
       </c>
-      <c r="J39" s="14" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>511,200</t>
         </is>
       </c>
-      <c r="K39" s="15" t="inlineStr">
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>1,136,000</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="13" customHeight="1">
-      <c r="A40" s="12" t="n"/>
-      <c r="B40" s="13" t="inlineStr">
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>ヤ10</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>(株)ヤマニ</t>
         </is>
       </c>
-      <c r="D40" s="14" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E40" s="14" t="n"/>
-      <c r="F40" s="14" t="inlineStr">
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="G40" s="14" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H40" s="14" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I40" s="14" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J40" s="14" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>158,080</t>
         </is>
       </c>
-      <c r="K40" s="15" t="inlineStr">
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>416,000</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="13" customHeight="1">
-      <c r="A41" s="12" t="n"/>
-      <c r="B41" s="13" t="inlineStr">
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>ル01</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>(株)ルック</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E41" s="14" t="n"/>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H41" s="14" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I41" s="14" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J41" s="14" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>74,970</t>
         </is>
       </c>
-      <c r="K41" s="15" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>166,600</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="13" customHeight="1">
-      <c r="A42" s="12" t="n"/>
-      <c r="B42" s="13" t="inlineStr">
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>シ15</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>関谷担当その他</t>
         </is>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>-1,900</t>
         </is>
       </c>
-      <c r="E42" s="14" t="n"/>
-      <c r="F42" s="16" t="inlineStr">
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>-1.5</t>
         </is>
       </c>
-      <c r="G42" s="14" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H42" s="14" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I42" s="14" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>167,525</t>
         </is>
       </c>
-      <c r="J42" s="14" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>126,000</t>
         </is>
       </c>
-      <c r="K42" s="15" t="inlineStr">
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>316,000</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="13" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>1課計</t>
         </is>
       </c>
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="18" t="n"/>
-      <c r="D43" s="19" t="inlineStr">
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>11,744,322</t>
         </is>
       </c>
-      <c r="E43" s="19" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>38.1</t>
         </is>
       </c>
-      <c r="F43" s="19" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>72.3</t>
         </is>
       </c>
-      <c r="G43" s="19" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>30,811,493</t>
         </is>
       </c>
-      <c r="H43" s="19" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>72.4</t>
         </is>
       </c>
-      <c r="I43" s="19" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>49,459,490</t>
         </is>
       </c>
-      <c r="J43" s="19" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>16,240,288</t>
         </is>
       </c>
-      <c r="K43" s="20" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>42,522,220</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="G2:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
